--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484273_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484273_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6387</v>
+        <v>2.3955</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9383</v>
+        <v>2.5044</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2996</v>
+        <v>-0.1089</v>
       </c>
       <c r="G2" t="n">
         <v>0.1817</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1522</v>
+        <v>-0.3955</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9546</v>
+        <v>-0.3885</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1976</v>
+        <v>-0.007</v>
       </c>
       <c r="V2" t="n">
         <v>1.8279</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5412</v>
+        <v>1.2957</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0512</v>
+        <v>0.5296</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.51</v>
+        <v>0.766</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4936</v>
+        <v>0.1985</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9504</v>
+        <v>-0.3407</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4568</v>
+        <v>0.5393</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8902</v>
+        <v>0.7572</v>
       </c>
       <c r="K3" t="n">
-        <v>4.0765</v>
+        <v>0.7572</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1863</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3966</v>
+        <v>-0.5587</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.1261</v>
+        <v>-1.098</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2704</v>
+        <v>0.5393</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4848</v>
+        <v>-0.2703</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5284</v>
+        <v>-0.2276</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0436</v>
+        <v>-0.0427</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3624</v>
+        <v>1.2364</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5622</v>
+        <v>3.2182</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1997</v>
+        <v>-1.9819</v>
       </c>
       <c r="G4" t="n">
         <v>-4.0882</v>
@@ -766,13 +766,13 @@
         <v>2.3441</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.182</v>
+        <v>-0.308</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.4207</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1052</v>
+        <v>0.1127</v>
       </c>
       <c r="V4" t="n">
         <v>4.2652</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8561</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2263</v>
+        <v>2.7072</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6298</v>
+        <v>-1.8641</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1985</v>
+        <v>0.4936</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3407</v>
+        <v>1.9504</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5393</v>
+        <v>-1.4568</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7572</v>
+        <v>2.8902</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7572</v>
+        <v>4.0765</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.1863</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5587</v>
+        <v>-2.3966</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.098</v>
+        <v>-2.1261</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5393</v>
+        <v>-0.2704</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7098</v>
+        <v>-0.2132</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5309</v>
+        <v>0.1845</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1789</v>
+        <v>-0.3977</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3553</v>
+        <v>0.7157</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2707</v>
+        <v>1.3001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.626</v>
+        <v>-0.5844</v>
       </c>
       <c r="G6" t="n">
-        <v>1.714</v>
+        <v>1.3049</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0944</v>
+        <v>-0.1517</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6196</v>
+        <v>1.4566</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3945</v>
+        <v>1.1899</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3136</v>
+        <v>0.0025</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0809</v>
+        <v>1.1873</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3195</v>
+        <v>0.115</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2192</v>
+        <v>-0.1542</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5387</v>
+        <v>0.2692</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3603</v>
+        <v>0.1486</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9839</v>
+        <v>0.1102</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6236</v>
+        <v>0.0384</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.9376</v>
+        <v>-2.1052</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.719</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0157</v>
+        <v>-1.1226</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4911</v>
+        <v>-1.5852</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4754</v>
+        <v>0.4626</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3049</v>
+        <v>1.714</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1517</v>
+        <v>1.0944</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4566</v>
+        <v>0.6196</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1899</v>
+        <v>1.3945</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0025</v>
+        <v>1.3136</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1873</v>
+        <v>0.0809</v>
       </c>
       <c r="M7" t="n">
-        <v>0.115</v>
+        <v>0.3195</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1542</v>
+        <v>-0.2192</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2692</v>
+        <v>0.5387</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3674</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5514</v>
+        <v>-0.1176</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6987</v>
+        <v>0.6694</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1473</v>
+        <v>-0.787</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1052</v>
+        <v>-1.9376</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.719</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1052</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1777</v>
+        <v>-1.6721</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8147</v>
+        <v>-0.3092</v>
       </c>
       <c r="F8" t="n">
         <v>-1.363</v>
@@ -1078,10 +1078,10 @@
         <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7208</v>
+        <v>-0.2153</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1816</v>
+        <v>0.324</v>
       </c>
       <c r="U8" t="n">
         <v>-0.5393</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4979</v>
+        <v>-2.0219</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8485</v>
+        <v>-1.2972</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6494</v>
+        <v>-0.7248</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.5081</v>
+        <v>-0.4982</v>
       </c>
       <c r="H9" t="n">
-        <v>-7.8837</v>
+        <v>-1.8598</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3756</v>
+        <v>1.3616</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.2929</v>
+        <v>-1.4968</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.2086</v>
+        <v>-2.1848</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9157</v>
+        <v>0.6879</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.2152</v>
+        <v>0.9986</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.6751</v>
+        <v>0.3249</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5401</v>
+        <v>0.6737</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6428</v>
+        <v>-0.227</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2258</v>
+        <v>0.6219</v>
       </c>
       <c r="U9" t="n">
-        <v>0.417</v>
+        <v>-0.8489</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2186</v>
+        <v>-1.8828</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5081</v>
+        <v>-3.0519</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7016</v>
+        <v>-2.2935</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8065</v>
+        <v>-0.7584</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4982</v>
+        <v>-6.5081</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8598</v>
+        <v>-7.8837</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3616</v>
+        <v>1.3756</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4968</v>
+        <v>-3.2929</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.1848</v>
+        <v>-5.2086</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6879</v>
+        <v>1.9157</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9986</v>
+        <v>-3.2152</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3249</v>
+        <v>-2.6751</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6737</v>
+        <v>-0.5401</v>
       </c>
       <c r="P10" t="n">
-        <v>0.586</v>
+        <v>2.1488</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7131</v>
+        <v>0.0888</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2175</v>
+        <v>-0.2192</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9306</v>
+        <v>0.308</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8828</v>
+        <v>1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5145</v>
+        <v>-4.4715</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1713</v>
+        <v>-4.2038</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3433</v>
+        <v>-0.2677</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.0274</v>
+        <v>-1.2179</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.2989</v>
+        <v>-0.7595</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7286</v>
+        <v>-0.4583</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2266</v>
+        <v>-1.9515</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.3075</v>
+        <v>-1.2241</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0809</v>
+        <v>-0.7274</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8008</v>
+        <v>0.7336</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9913</v>
+        <v>0.4646</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8095</v>
+        <v>0.269</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>0.005</v>
+        <v>-0.7848000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2805</v>
+        <v>0.3653</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2855</v>
+        <v>-1.1501</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6642</v>
+        <v>-1.8828</v>
       </c>
       <c r="W11" t="n">
         <v>-0.6642</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7361</v>
+        <v>-4.5085</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3049</v>
+        <v>-3.1108</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4312</v>
+        <v>-1.3977</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2179</v>
+        <v>-5.0274</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7595</v>
+        <v>-4.2989</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4583</v>
+        <v>-0.7286</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9515</v>
+        <v>-2.2266</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2241</v>
+        <v>-2.3075</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7274</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7336</v>
+        <v>-2.8008</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4646</v>
+        <v>-1.9913</v>
       </c>
       <c r="O12" t="n">
-        <v>0.269</v>
+        <v>-0.8095</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0493</v>
+        <v>0.0111</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2642</v>
+        <v>-0.22</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3136</v>
+        <v>0.231</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8828</v>
+        <v>-0.6642</v>
       </c>
       <c r="W12" t="n">
         <v>-0.6642</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.6649</v>
+        <v>-10.362</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.842600000000001</v>
+        <v>-2.540200000000001</v>
       </c>
       <c r="F13" t="n">
         <v>-7.8223</v>
@@ -1441,13 +1441,13 @@
         <v>2.0213</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.473</v>
+        <v>-2.473000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>-4.5002</v>
       </c>
       <c r="L13" t="n">
-        <v>2.027200000000001</v>
+        <v>2.0272</v>
       </c>
       <c r="M13" t="n">
         <v>-11.4078</v>
@@ -1456,7 +1456,7 @@
         <v>-11.4017</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.006000000000000227</v>
+        <v>-0.005999999999999783</v>
       </c>
       <c r="P13" t="n">
         <v>8.7905</v>
@@ -1468,10 +1468,10 @@
         <v>17.5809</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.585699999999999</v>
+        <v>-2.2832</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4967000000000001</v>
+        <v>0.7992999999999997</v>
       </c>
       <c r="U13" t="n">
         <v>-3.0826</v>
@@ -1480,7 +1480,7 @@
         <v>-2.988799999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>7.923999999999999</v>
+        <v>7.924</v>
       </c>
       <c r="X13" t="n">
         <v>-10.9127</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.0818</v>
+        <v>10.8681</v>
       </c>
       <c r="E14" t="n">
-        <v>11.6084</v>
+        <v>10.6983</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4735</v>
+        <v>0.1698</v>
       </c>
       <c r="G14" t="n">
         <v>9.3613</v>
@@ -1546,13 +1546,13 @@
         <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8926</v>
+        <v>1.6789</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8629</v>
+        <v>0.9528</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0297</v>
+        <v>0.7261</v>
       </c>
       <c r="V14" t="n">
         <v>0.6093</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3646</v>
+        <v>3.691</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3101</v>
+        <v>1.7146</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0545</v>
+        <v>1.9764</v>
       </c>
       <c r="G15" t="n">
         <v>2.5597</v>
@@ -1624,13 +1624,13 @@
         <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.171</v>
+        <v>0.1554</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1594</v>
+        <v>0.245</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0116</v>
+        <v>-0.0896</v>
       </c>
       <c r="V15" t="n">
         <v>3.7107</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7433</v>
+        <v>1.7121</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2276</v>
+        <v>1.3986</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4843</v>
+        <v>0.3135</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7579</v>
+        <v>4.9141</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5285</v>
+        <v>4.4554</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2294</v>
+        <v>0.4587</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0609</v>
+        <v>5.2833</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0205</v>
+        <v>4.6892</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>0.5942</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8188</v>
+        <v>-0.3692</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.549</v>
+        <v>-0.2338</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2698</v>
+        <v>-0.1354</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R16" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9151</v>
+        <v>0.1691</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1666</v>
+        <v>0.0221</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2515</v>
+        <v>0.147</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.4372</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5897</v>
+        <v>-0.5683</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0711</v>
+        <v>1.0055</v>
       </c>
       <c r="G17" t="n">
-        <v>4.9141</v>
+        <v>1.5375</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4554</v>
+        <v>2.6567</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4587</v>
+        <v>-1.1192</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2833</v>
+        <v>0.2239</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6892</v>
+        <v>1.4773</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5942</v>
+        <v>-1.2535</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3692</v>
+        <v>1.3136</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2338</v>
+        <v>1.1794</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1354</v>
+        <v>0.1342</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.5395</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8822</v>
+        <v>0.5323</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.1845</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0954</v>
+        <v>0.3478</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8317</v>
+        <v>-1.8279</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8317</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3273</v>
+        <v>0.2447</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.6696</v>
+        <v>-0.4049</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3423</v>
+        <v>0.6496</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9384</v>
+        <v>0.2166</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3654</v>
+        <v>0.1359</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.3038</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9782999999999999</v>
+        <v>-0.1634</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5157</v>
+        <v>-0.2443</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.4941</v>
+        <v>0.0809</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0399</v>
+        <v>0.38</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8496</v>
+        <v>0.3802</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8097</v>
+        <v>-0.0002</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-1.9534</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>0.959</v>
+        <v>0.0048</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0384</v>
+        <v>0.4933</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9974</v>
+        <v>-0.4885</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6056</v>
+        <v>0.6093</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>1.3283</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3445</v>
+        <v>-0.0384</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9728</v>
+        <v>0.4186</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6283</v>
+        <v>-0.457</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5375</v>
+        <v>-0.7579</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6567</v>
+        <v>-0.5285</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1192</v>
+        <v>-0.2294</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2239</v>
+        <v>0.0609</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4773</v>
+        <v>0.0205</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2535</v>
+        <v>0.0405</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3136</v>
+        <v>-0.8188</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1794</v>
+        <v>-0.549</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1342</v>
+        <v>-0.2698</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2494</v>
+        <v>0.1335</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.22</v>
+        <v>0.3577</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0294</v>
+        <v>-0.2242</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5475</v>
+        <v>-0.1671</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7083</v>
+        <v>0.8819</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1607</v>
+        <v>-1.049</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2166</v>
+        <v>-2.7997</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1359</v>
+        <v>-1.8826</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08069999999999999</v>
+        <v>-0.9171</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1634</v>
+        <v>-1.5611</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2443</v>
+        <v>-1.5887</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0809</v>
+        <v>0.0276</v>
       </c>
       <c r="M20" t="n">
-        <v>0.38</v>
+        <v>-1.2386</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3802</v>
+        <v>-0.2939</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0002</v>
+        <v>-0.9447</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.586</v>
+        <v>0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7874</v>
+        <v>0.7731</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1899</v>
+        <v>0.615</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9772999999999999</v>
+        <v>0.1581</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6093</v>
+        <v>1.2735</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>1.8279</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6093</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5627</v>
+        <v>-0.3055</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0841</v>
+        <v>-3.2652</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6468</v>
+        <v>2.9597</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7997</v>
+        <v>-0.9384</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8826</v>
+        <v>2.3654</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9171</v>
+        <v>-3.3038</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5611</v>
+        <v>-0.9782999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5887</v>
+        <v>1.5157</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0276</v>
+        <v>-2.4941</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2386</v>
+        <v>0.0399</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2939</v>
+        <v>0.8496</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9447</v>
+        <v>-0.8097</v>
       </c>
       <c r="P21" t="n">
-        <v>0.586</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3775</v>
+        <v>0.9808</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8173</v>
+        <v>0.3661</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4397</v>
+        <v>0.6147</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2735</v>
+        <v>1.6056</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8279</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5545</v>
+        <v>1.3283</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4037</v>
+        <v>-3.755</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.647</v>
+        <v>-3.0514</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7567</v>
+        <v>-0.7036</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2125</v>
@@ -2170,13 +2170,13 @@
         <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5316</v>
+        <v>0.1802</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2504</v>
+        <v>-0.154</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2811</v>
+        <v>0.3342</v>
       </c>
       <c r="V22" t="n">
         <v>-2.16</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10.6648</v>
+        <v>12.6871</v>
       </c>
       <c r="E23" t="n">
-        <v>7.822199999999999</v>
+        <v>7.8222</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8426</v>
+        <v>4.8649</v>
       </c>
       <c r="G23" t="n">
         <v>13.8807</v>
@@ -2227,7 +2227,7 @@
         <v>11.4017</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005899999999999572</v>
+        <v>0.00590000000000046</v>
       </c>
       <c r="M23" t="n">
         <v>2.473</v>
@@ -2248,22 +2248,22 @@
         <v>8.7905</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5858</v>
+        <v>4.6081</v>
       </c>
       <c r="T23" t="n">
         <v>3.0825</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4966999999999998</v>
+        <v>1.5256</v>
       </c>
       <c r="V23" t="n">
-        <v>2.988799999999999</v>
+        <v>2.9888</v>
       </c>
       <c r="W23" t="n">
         <v>10.9127</v>
       </c>
       <c r="X23" t="n">
-        <v>-7.924100000000001</v>
+        <v>-7.924099999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484273_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484273_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>-1.8279</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.7157</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7072</v>
+        <v>1.3001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8641</v>
+        <v>-0.5844</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4936</v>
+        <v>1.3049</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9504</v>
+        <v>-0.1517</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4568</v>
+        <v>1.4566</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8902</v>
+        <v>1.1899</v>
       </c>
       <c r="K5" t="n">
-        <v>4.0765</v>
+        <v>0.0025</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1863</v>
+        <v>1.1873</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3966</v>
+        <v>0.115</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.1261</v>
+        <v>-0.1542</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2704</v>
+        <v>0.2692</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2132</v>
+        <v>0.1486</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1845</v>
+        <v>0.1102</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3977</v>
+        <v>0.0384</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6093</v>
+        <v>-2.1052</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7157</v>
+        <v>0.614</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3001</v>
+        <v>0.614</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5844</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3049</v>
+        <v>0.614</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1517</v>
+        <v>0.614</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4566</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1899</v>
+        <v>0.614</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0025</v>
+        <v>0.614</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1873</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.115</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1542</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2692</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1486</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1102</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0384</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1226</v>
+        <v>0.2292</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5852</v>
+        <v>2.0933</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4626</v>
+        <v>-1.8641</v>
       </c>
       <c r="G7" t="n">
-        <v>1.714</v>
+        <v>-0.1204</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0944</v>
+        <v>1.3364</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6196</v>
+        <v>-1.4568</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3945</v>
+        <v>2.2762</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3136</v>
+        <v>3.4625</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0809</v>
+        <v>-1.1863</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3195</v>
+        <v>-2.3966</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2192</v>
+        <v>-2.1261</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5387</v>
+        <v>-0.2704</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
         <v>2.1488</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1176</v>
+        <v>-0.2132</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6694</v>
+        <v>0.1845</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.787</v>
+        <v>-0.3977</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.9376</v>
+        <v>-0.6093</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.719</v>
+        <v>0.6093</v>
       </c>
       <c r="X7" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. VERA CUSCOLL</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6721</v>
+        <v>-1.1226</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3092</v>
+        <v>-1.5852</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.363</v>
+        <v>0.4626</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4336</v>
+        <v>1.714</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1059</v>
+        <v>1.0944</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5395</v>
+        <v>0.6196</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6332</v>
+        <v>1.3945</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0409</v>
+        <v>1.3136</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6741</v>
+        <v>0.0809</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1996</v>
+        <v>0.3195</v>
       </c>
       <c r="N8" t="n">
-        <v>0.065</v>
+        <v>-0.2192</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1346</v>
+        <v>0.5387</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2153</v>
+        <v>-0.1176</v>
       </c>
       <c r="T8" t="n">
-        <v>0.324</v>
+        <v>0.6694</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5393</v>
+        <v>-0.787</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>-1.9376</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.719</v>
       </c>
       <c r="X8" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>E. VERA CUSCOLL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0219</v>
+        <v>-1.6721</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2972</v>
+        <v>-0.3092</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7248</v>
+        <v>-1.363</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4982</v>
+        <v>-0.4336</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8598</v>
+        <v>0.1059</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3616</v>
+        <v>-0.5395</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4968</v>
+        <v>-0.6332</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.1848</v>
+        <v>0.0409</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6879</v>
+        <v>-0.6741</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9986</v>
+        <v>0.1996</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3249</v>
+        <v>0.065</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6737</v>
+        <v>0.1346</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.227</v>
+        <v>-0.2153</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6219</v>
+        <v>0.324</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8489</v>
+        <v>-0.5393</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8828</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4373</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0519</v>
+        <v>-2.0219</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2935</v>
+        <v>-1.2972</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7584</v>
+        <v>-0.7248</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.5081</v>
+        <v>-0.4982</v>
       </c>
       <c r="H10" t="n">
-        <v>-7.8837</v>
+        <v>-1.8598</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3756</v>
+        <v>1.3616</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.2929</v>
+        <v>-1.4968</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.2086</v>
+        <v>-2.1848</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9157</v>
+        <v>0.6879</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.2152</v>
+        <v>0.9986</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.6751</v>
+        <v>0.3249</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5401</v>
+        <v>0.6737</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0888</v>
+        <v>-0.227</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2192</v>
+        <v>0.6219</v>
       </c>
       <c r="U10" t="n">
-        <v>0.308</v>
+        <v>-0.8489</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2186</v>
+        <v>-1.8828</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4715</v>
+        <v>-3.0519</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2038</v>
+        <v>-2.2935</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2677</v>
+        <v>-0.7584</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2179</v>
+        <v>-6.5081</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7595</v>
+        <v>-7.8837</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4583</v>
+        <v>1.3756</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9515</v>
+        <v>-3.2929</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2241</v>
+        <v>-5.2086</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7274</v>
+        <v>1.9157</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7336</v>
+        <v>-3.2152</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4646</v>
+        <v>-2.6751</v>
       </c>
       <c r="O11" t="n">
-        <v>0.269</v>
+        <v>-0.5401</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.586</v>
+        <v>2.1488</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7848000000000001</v>
+        <v>0.0888</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3653</v>
+        <v>-0.2192</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1501</v>
+        <v>0.308</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8828</v>
+        <v>1.2186</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5085</v>
+        <v>-4.4715</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1108</v>
+        <v>-4.2038</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3977</v>
+        <v>-0.2677</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.0274</v>
+        <v>-1.2179</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.2989</v>
+        <v>-0.7595</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7286</v>
+        <v>-0.4583</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2266</v>
+        <v>-1.9515</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.3075</v>
+        <v>-1.2241</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0809</v>
+        <v>-0.7274</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8008</v>
+        <v>0.7336</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.9913</v>
+        <v>0.4646</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8095</v>
+        <v>0.269</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0111</v>
+        <v>-0.7848000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.22</v>
+        <v>0.3653</v>
       </c>
       <c r="U12" t="n">
-        <v>0.231</v>
+        <v>-1.1501</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6642</v>
+        <v>-1.8828</v>
       </c>
       <c r="W12" t="n">
         <v>-0.6642</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.362</v>
+        <v>-4.5085</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.540200000000001</v>
+        <v>-3.1108</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.8223</v>
+        <v>-1.3977</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.8807</v>
+        <v>-5.0274</v>
       </c>
       <c r="H13" t="n">
-        <v>-15.9019</v>
+        <v>-4.2989</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0213</v>
+        <v>-0.7286</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.473000000000001</v>
+        <v>-2.2266</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.5002</v>
+        <v>-2.3075</v>
       </c>
       <c r="L13" t="n">
-        <v>2.0272</v>
+        <v>0.0809</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.4078</v>
+        <v>-2.8008</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.4017</v>
+        <v>-1.9913</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.005999999999999783</v>
+        <v>-0.8095</v>
       </c>
       <c r="P13" t="n">
-        <v>8.7905</v>
+        <v>1.1721</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.7903</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>17.5809</v>
+        <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2832</v>
+        <v>0.0111</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7992999999999997</v>
+        <v>-0.22</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.0826</v>
+        <v>0.231</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.988799999999999</v>
+        <v>-0.6642</v>
       </c>
       <c r="W13" t="n">
-        <v>7.924</v>
+        <v>-0.6642</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.9127</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.8681</v>
+        <v>-10.362</v>
       </c>
       <c r="E14" t="n">
-        <v>10.6983</v>
+        <v>-2.5401</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1698</v>
+        <v>-7.8223</v>
       </c>
       <c r="G14" t="n">
-        <v>9.3613</v>
+        <v>-13.8807</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5058</v>
+        <v>-15.9019</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8555</v>
+        <v>2.0213</v>
       </c>
       <c r="J14" t="n">
-        <v>8.042999999999999</v>
+        <v>-2.473000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>3.0519</v>
+        <v>-4.5002</v>
       </c>
       <c r="L14" t="n">
-        <v>4.9911</v>
+        <v>2.0272</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3183</v>
+        <v>-11.4078</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4539</v>
+        <v>-11.4017</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1356</v>
+        <v>-0.006000000000000005</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7814</v>
+        <v>8.7905</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-8.7903</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1721</v>
+        <v>17.5809</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6789</v>
+        <v>-2.2832</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9528</v>
+        <v>0.7993000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7261</v>
+        <v>-3.0826</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6093</v>
+        <v>-2.9888</v>
       </c>
       <c r="W14" t="n">
-        <v>3.6559</v>
+        <v>7.924</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.0466</v>
-      </c>
+        <v>-10.9127</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.691</v>
+        <v>10.5612</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7146</v>
+        <v>10.3913</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9764</v>
+        <v>0.1698</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5597</v>
+        <v>9.0543</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9637</v>
+        <v>4.1988</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4041</v>
+        <v>4.8555</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1112</v>
+        <v>7.7361</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7843</v>
+        <v>2.7449</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6731</v>
+        <v>4.9911</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4484</v>
+        <v>1.3183</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1794</v>
+        <v>1.4539</v>
       </c>
       <c r="O15" t="n">
-        <v>0.269</v>
+        <v>-0.1356</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.7348</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
         <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1554</v>
+        <v>1.6789</v>
       </c>
       <c r="T15" t="n">
-        <v>0.245</v>
+        <v>0.9528</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0896</v>
+        <v>0.7261</v>
       </c>
       <c r="V15" t="n">
-        <v>3.7107</v>
+        <v>0.6093</v>
       </c>
       <c r="W15" t="n">
-        <v>4.2652</v>
+        <v>3.6559</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5545</v>
+        <v>-3.0466</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7121</v>
+        <v>3.691</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3986</v>
+        <v>1.7146</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3135</v>
+        <v>1.9764</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9141</v>
+        <v>2.5597</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4554</v>
+        <v>2.9637</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4587</v>
+        <v>-0.4041</v>
       </c>
       <c r="J16" t="n">
-        <v>5.2833</v>
+        <v>1.1112</v>
       </c>
       <c r="K16" t="n">
-        <v>4.6892</v>
+        <v>1.7843</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5942</v>
+        <v>-0.6731</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3692</v>
+        <v>1.4484</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2338</v>
+        <v>1.1794</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1354</v>
+        <v>0.269</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.5395</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.9069</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1691</v>
+        <v>0.1554</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0221</v>
+        <v>0.245</v>
       </c>
       <c r="U16" t="n">
-        <v>0.147</v>
+        <v>-0.0896</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8317</v>
+        <v>3.7107</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.2652</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8317</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4372</v>
+        <v>1.7121</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5683</v>
+        <v>1.3986</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0055</v>
+        <v>0.3135</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5375</v>
+        <v>4.9141</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6567</v>
+        <v>4.4554</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1192</v>
+        <v>0.4587</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2239</v>
+        <v>5.2833</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4773</v>
+        <v>4.6892</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2535</v>
+        <v>0.5942</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3136</v>
+        <v>-0.3692</v>
       </c>
       <c r="N17" t="n">
-        <v>1.1794</v>
+        <v>-0.2338</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1342</v>
+        <v>-0.1354</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5323</v>
+        <v>0.1691</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1845</v>
+        <v>0.0221</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3478</v>
+        <v>0.147</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8279</v>
+        <v>-0.8317</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8279</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2447</v>
+        <v>0.4372</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4049</v>
+        <v>-0.5683</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6496</v>
+        <v>1.0055</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2166</v>
+        <v>1.5375</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1359</v>
+        <v>2.6567</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08069999999999999</v>
+        <v>-1.1192</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1634</v>
+        <v>0.2239</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2443</v>
+        <v>1.4773</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>-1.2535</v>
       </c>
       <c r="M18" t="n">
-        <v>0.38</v>
+        <v>1.3136</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3802</v>
+        <v>1.1794</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0002</v>
+        <v>0.1342</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0048</v>
+        <v>0.5323</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4933</v>
+        <v>0.1845</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4885</v>
+        <v>0.3478</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6093</v>
+        <v>-1.8279</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6093</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0384</v>
+        <v>0.307</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4186</v>
+        <v>0.307</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.457</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7579</v>
+        <v>0.307</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5285</v>
+        <v>0.307</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2294</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0609</v>
+        <v>0.307</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0205</v>
+        <v>0.307</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8188</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.549</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2698</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1335</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3577</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2242</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,12 +2038,17 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1671</v>
+        <v>0.2447</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8819</v>
+        <v>-0.4049</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.049</v>
+        <v>0.6496</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7997</v>
+        <v>0.2166</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8826</v>
+        <v>0.1359</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9171</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5611</v>
+        <v>-0.1634</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.5887</v>
+        <v>-0.2443</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0276</v>
+        <v>0.0809</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2386</v>
+        <v>0.38</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2939</v>
+        <v>0.3802</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9447</v>
+        <v>-0.0002</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>-0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7731</v>
+        <v>0.0048</v>
       </c>
       <c r="T20" t="n">
-        <v>0.615</v>
+        <v>0.4933</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1581</v>
+        <v>-0.4885</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2735</v>
+        <v>0.6093</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8279</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5545</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3055</v>
+        <v>-0.0384</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2652</v>
+        <v>0.4186</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9597</v>
+        <v>-0.457</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9384</v>
+        <v>-0.7579</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3654</v>
+        <v>-0.5285</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.3038</v>
+        <v>-0.2294</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9782999999999999</v>
+        <v>0.0609</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5157</v>
+        <v>0.0205</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.4941</v>
+        <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0399</v>
+        <v>-0.8188</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8496</v>
+        <v>-0.549</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8097</v>
+        <v>-0.2698</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9808</v>
+        <v>0.1335</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3661</v>
+        <v>0.3577</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6147</v>
+        <v>-0.2242</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6056</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.3283</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.755</v>
+        <v>-0.1671</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0514</v>
+        <v>0.8819</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7036</v>
+        <v>-1.049</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2125</v>
+        <v>-2.7997</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2303</v>
+        <v>-1.8826</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4428</v>
+        <v>-0.9171</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6119</v>
+        <v>-1.5611</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6958</v>
+        <v>-1.5887</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3077</v>
+        <v>0.0276</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3994</v>
+        <v>-1.2386</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5344</v>
+        <v>-0.2939</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.135</v>
+        <v>-0.9447</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1802</v>
+        <v>0.7731</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.154</v>
+        <v>0.615</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3342</v>
+        <v>0.1581</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.16</v>
+        <v>1.2735</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3321</v>
+        <v>1.8279</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8279</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,235 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>12.6871</v>
+        <v>-0.3055</v>
       </c>
       <c r="E23" t="n">
-        <v>7.8222</v>
+        <v>-3.2652</v>
       </c>
       <c r="F23" t="n">
+        <v>2.9597</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.9384</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.3654</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-3.3038</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.9782999999999999</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.5157</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-2.4941</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.0399</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.8496</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.8097</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.6147</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.6056</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.3283</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>L. ANDUJAR MASCARO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-3.755</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.0514</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.7036</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.2125</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.2303</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.4428</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.6119</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.6958</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.3077</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.5344</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.135</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1802</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.154</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484273_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12.6872</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.822199999999998</v>
+      </c>
+      <c r="F25" t="n">
         <v>4.8649</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G25" t="n">
         <v>13.8807</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H25" t="n">
         <v>15.9021</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I25" t="n">
         <v>-2.0215</v>
       </c>
-      <c r="J23" t="n">
-        <v>11.4076</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="J25" t="n">
+        <v>11.4077</v>
+      </c>
+      <c r="K25" t="n">
         <v>11.4017</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
         <v>0.00590000000000046</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M25" t="n">
         <v>2.473</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N25" t="n">
         <v>4.5002</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O25" t="n">
         <v>-2.0272</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P25" t="n">
         <v>-8.7905</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q25" t="n">
         <v>-17.5808</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>8.7905</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>4.6081</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>3.0825</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>1.5256</v>
       </c>
-      <c r="V23" t="n">
-        <v>2.9888</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="V25" t="n">
+        <v>2.988799999999999</v>
+      </c>
+      <c r="W25" t="n">
         <v>10.9127</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X25" t="n">
         <v>-7.924099999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
